--- a/artfynd/A 41770-2024 artfynd.xlsx
+++ b/artfynd/A 41770-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113120903</v>
+        <v>113120906</v>
       </c>
       <c r="B2" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514616</v>
+        <v>514581</v>
       </c>
       <c r="R2" t="n">
-        <v>7006401</v>
+        <v>7006483</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113120907</v>
+        <v>113120902</v>
       </c>
       <c r="B3" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514552</v>
+        <v>514758</v>
       </c>
       <c r="R3" t="n">
-        <v>7006461</v>
+        <v>7006442</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,6 +870,208 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113120903</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Råkberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>514616</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7006401</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113120907</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Råkberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>514552</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7006461</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 41770-2024 artfynd.xlsx
+++ b/artfynd/A 41770-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113120906</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113120902</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113120903</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,8 +1096,19 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113120907</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>